--- a/public/股票交易匯入範本.xlsx
+++ b/public/股票交易匯入範本.xlsx
@@ -2,28 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17280" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交易記錄" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="說明" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="#,##0.##"/>
   </numFmts>
   <fonts count="11">
     <font>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
@@ -31,59 +29,69 @@
     </font>
     <font>
       <name val="Arial"/>
+      <family val="2"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
-      <i val="1"/>
-      <color rgb="0094A3B8"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="001E293B"/>
+      <family val="2"/>
+      <color rgb="FF1E293B"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
+      <family val="2"/>
       <b val="1"/>
-      <color rgb="004F46E5"/>
+      <color rgb="FF4F46E5"/>
       <sz val="13"/>
     </font>
     <font>
       <name val="Arial"/>
+      <family val="2"/>
       <b val="1"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
+      <family val="2"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="0064748B"/>
+      <family val="2"/>
+      <color rgb="FF64748B"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="00EF4444"/>
+      <family val="2"/>
+      <color rgb="FFEF4444"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
+      <family val="2"/>
       <b val="1"/>
-      <color rgb="004F46E5"/>
+      <color rgb="FF4F46E5"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="00475569"/>
+      <family val="2"/>
+      <color rgb="FF475569"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="新細明體"/>
+      <charset val="136"/>
+      <family val="3"/>
+      <sz val="9"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -92,22 +100,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004F46E5"/>
+        <fgColor rgb="FF4F46E5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EEF2FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F8FAFC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
+        <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -121,55 +119,57 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00E2E8F0"/>
+        <color rgb="FFE2E8F0"/>
       </left>
       <right style="thin">
-        <color rgb="00E2E8F0"/>
+        <color rgb="FFE2E8F0"/>
       </right>
       <top style="thin">
-        <color rgb="00E2E8F0"/>
+        <color rgb="FFE2E8F0"/>
       </top>
       <bottom style="thin">
-        <color rgb="00E2E8F0"/>
+        <color rgb="FFE2E8F0"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -532,18 +532,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" style="13" min="1" max="1"/>
+    <col width="8" customWidth="1" style="13" min="2" max="2"/>
+    <col width="10" customWidth="1" style="13" min="3" max="3"/>
+    <col width="16" customWidth="1" style="13" min="4" max="4"/>
+    <col width="10" customWidth="1" style="13" min="5" max="5"/>
+    <col width="12" customWidth="1" style="13" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="30" customHeight="1" s="13">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>日期</t>
@@ -575,383 +575,149 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>YYYY-MM-DD</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>買 或 賣</t>
+    <row r="2">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>2024-01-15</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>買</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>可留空</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>股票名稱</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>整數股數</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>每股價格</t>
-        </is>
+          <t>0050</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>元大台灣50</t>
+        </is>
+      </c>
+      <c r="E2" s="15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F2" s="15" t="n">
+        <v>185.5</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>2024-01-15</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>2024-03-20</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>買</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>2330</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="E3" s="15" t="n">
+        <v>500</v>
+      </c>
+      <c r="F3" s="15" t="n">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1" s="13">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>賣</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>0050</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>元大台灣50</t>
         </is>
       </c>
-      <c r="E3" s="7" t="n">
+      <c r="E4" s="15" t="n">
+        <v>500</v>
+      </c>
+      <c r="F4" s="15" t="n">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1" s="13">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>2024-08-05</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>買</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>00662</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>富邦NASDAQ</t>
+        </is>
+      </c>
+      <c r="E5" s="15" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F5" s="15" t="n">
+        <v>42.3</v>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1" s="13">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>2024-11-18</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>買</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>2412</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>中華電</t>
+        </is>
+      </c>
+      <c r="E6" s="15" t="n">
         <v>1000</v>
       </c>
-      <c r="F3" s="7" t="n">
-        <v>185.5</v>
+      <c r="F6" s="15" t="n">
+        <v>125.5</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>2024-03-20</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>買</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>2330</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>台積電</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="n">
-        <v>500</v>
-      </c>
-      <c r="F4" s="7" t="n">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>2024-06-10</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>賣</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>0050</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>元大台灣50</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="n">
-        <v>500</v>
-      </c>
-      <c r="F5" s="7" t="n">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>2024-08-05</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>買</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>00662</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>富邦NASDAQ</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="n">
-        <v>2000</v>
-      </c>
-      <c r="F6" s="7" t="n">
-        <v>42.3</v>
-      </c>
-    </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>2024-11-18</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>買</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>2412</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>中華電</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F7" s="7" t="n">
-        <v>125.5</v>
-      </c>
-    </row>
-    <row r="8" ht="22" customHeight="1"/>
-    <row r="9" ht="22" customHeight="1"/>
+    <row r="7" ht="22" customHeight="1" s="13"/>
+    <row r="8" ht="22" customHeight="1" s="13"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="8" t="inlineStr">
-        <is>
-          <t>欄位說明</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="9" t="inlineStr">
-        <is>
-          <t>欄位</t>
-        </is>
-      </c>
-      <c r="B3" s="10" t="inlineStr">
-        <is>
-          <t>說明</t>
-        </is>
-      </c>
-      <c r="C3" s="11" t="inlineStr">
-        <is>
-          <t>必填</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="10" t="inlineStr">
-        <is>
-          <t>日期</t>
-        </is>
-      </c>
-      <c r="B4" s="10" t="inlineStr">
-        <is>
-          <t>YYYY-MM-DD 格式，例：2024-01-15</t>
-        </is>
-      </c>
-      <c r="C4" s="12" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="10" t="inlineStr">
-        <is>
-          <t>類別</t>
-        </is>
-      </c>
-      <c r="B5" s="10" t="inlineStr">
-        <is>
-          <t>輸入「買」或「賣」</t>
-        </is>
-      </c>
-      <c r="C5" s="12" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="10" t="inlineStr">
-        <is>
-          <t>代號</t>
-        </is>
-      </c>
-      <c r="B6" s="10" t="inlineStr">
-        <is>
-          <t>股票代號，例：0050、2330（可留空，系統自動查詢）</t>
-        </is>
-      </c>
-      <c r="C6" s="11" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>名稱</t>
-        </is>
-      </c>
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>股票名稱，例：元大台灣50</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>股數</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>交易股數（整數）</t>
-        </is>
-      </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>單價</t>
-        </is>
-      </c>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>每股成交價格</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="13" t="inlineStr">
-        <is>
-          <t>注意事項</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="14" t="inlineStr">
-        <is>
-          <t>• 第一列為標題列，不可刪除或修改欄位名稱</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="14" t="inlineStr">
-        <is>
-          <t>• 第二列為說明列，匯入時會自動略過</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="14" t="inlineStr">
-        <is>
-          <t>• 代號欄位留空時，系統會依名稱自動查詢代號</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="14" t="inlineStr">
-        <is>
-          <t>• ETF 代號以 0 開頭（如 0050、00662）</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="14" t="inlineStr">
-        <is>
-          <t>• 股數請填整數，不需加千分位逗號</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="14" t="inlineStr">
-        <is>
-          <t>• 日期格式必須為 YYYY-MM-DD</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="A16:C16"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>